--- a/DEV/org.openl.rules/test/rules/binding/ArrayMethodsTest.xlsx
+++ b/DEV/org.openl.rules/test/rules/binding/ArrayMethodsTest.xlsx
@@ -96,7 +96,7 @@
     <t>return Name(getPersons());</t>
   </si>
   <si>
-    <t>for(int i = 0; i&lt; personProfile.length; i++) {
+    <t>for(int i = 0; i&lt; personProfile.length; i += 1) {
 pp[i] = personProfile[i];
 }
 return pp;</t>
@@ -152,7 +152,7 @@
     <t>Method void test(int a)</t>
   </si>
   <si>
-    <t>a++;</t>
+    <t>a += 1;</t>
   </si>
   <si>
     <t>VAR</t>
